--- a/data/atm_operational_units.xlsx
+++ b/data/atm_operational_units.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oburdash\dev\repos\standard_inputs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3952DDC-D002-41CD-B1E4-0A42482E8CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE7154A-6077-4040-A9EF-A462FDE7E15F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -411,7 +411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -690,6 +690,75 @@
         <v>639</v>
       </c>
     </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2022</v>
+      </c>
+      <c r="B13">
+        <v>38</v>
+      </c>
+      <c r="C13">
+        <v>60</v>
+      </c>
+      <c r="D13">
+        <v>279</v>
+      </c>
+      <c r="E13">
+        <v>385</v>
+      </c>
+      <c r="F13">
+        <v>70</v>
+      </c>
+      <c r="G13">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2023</v>
+      </c>
+      <c r="B14">
+        <v>38</v>
+      </c>
+      <c r="C14">
+        <v>60</v>
+      </c>
+      <c r="D14">
+        <v>280</v>
+      </c>
+      <c r="E14">
+        <v>387</v>
+      </c>
+      <c r="F14">
+        <v>66</v>
+      </c>
+      <c r="G14">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2024</v>
+      </c>
+      <c r="B15">
+        <v>38</v>
+      </c>
+      <c r="C15">
+        <v>60</v>
+      </c>
+      <c r="D15">
+        <v>278</v>
+      </c>
+      <c r="E15">
+        <v>385</v>
+      </c>
+      <c r="F15">
+        <v>68</v>
+      </c>
+      <c r="G15">
+        <v>681</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -697,15 +766,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100763DCA751E988E49B18D7A5F3E2E0A59" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7de07ceb4021a46e644f2475dce3c08e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd" xmlns:ns3="c78a888a-83d8-49bb-8890-6eb97e8a3c0e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1a575a7fa9043b0502b32047f1ff6be7" ns2:_="" ns3:_="">
     <xsd:import namespace="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
@@ -928,6 +988,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -935,14 +1004,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54067D7D-C28A-4209-86CF-353F7FAF20CA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A7A9A02-2406-40F7-A731-DFDF0860EC76}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -961,6 +1022,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54067D7D-C28A-4209-86CF-353F7FAF20CA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1AA5E47-91CA-4FF6-A346-96717D8A5700}">
   <ds:schemaRefs>
@@ -976,4 +1045,10 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{fd60f3b8-f236-4830-aecc-da0a7fc54679}" enabled="1" method="Standard" siteId="{76f33c20-5979-4408-adf7-8b3c4be95e52}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>